--- a/Shablon/TDS2024C.xlsx
+++ b/Shablon/TDS2024C.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="419">
   <si>
     <t>50 нс/дел</t>
   </si>
@@ -948,267 +948,69 @@
     <t>ti1_1</t>
   </si>
   <si>
-    <t>ti2_1</t>
-  </si>
-  <si>
-    <t>ti3_1</t>
-  </si>
-  <si>
-    <t>ti4_1</t>
-  </si>
-  <si>
     <t>ti1_2</t>
   </si>
   <si>
-    <t>ti2_2</t>
-  </si>
-  <si>
-    <t>ti3_2</t>
-  </si>
-  <si>
-    <t>ti4_2</t>
-  </si>
-  <si>
     <t>ti1_3</t>
   </si>
   <si>
-    <t>ti2_3</t>
-  </si>
-  <si>
-    <t>ti3_3</t>
-  </si>
-  <si>
-    <t>ti4_3</t>
-  </si>
-  <si>
     <t>ti1_4</t>
   </si>
   <si>
-    <t>ti2_4</t>
-  </si>
-  <si>
-    <t>ti3_4</t>
-  </si>
-  <si>
-    <t>ti4_4</t>
-  </si>
-  <si>
     <t>ti1_5</t>
   </si>
   <si>
-    <t>ti2_5</t>
-  </si>
-  <si>
-    <t>ti3_5</t>
-  </si>
-  <si>
-    <t>ti4_5</t>
-  </si>
-  <si>
     <t>ti1_6</t>
   </si>
   <si>
-    <t>ti2_6</t>
-  </si>
-  <si>
-    <t>ti3_6</t>
-  </si>
-  <si>
-    <t>ti4_6</t>
-  </si>
-  <si>
     <t>ti1_7</t>
   </si>
   <si>
-    <t>ti2_7</t>
-  </si>
-  <si>
-    <t>ti3_7</t>
-  </si>
-  <si>
-    <t>ti4_7</t>
-  </si>
-  <si>
     <t>ti1_8</t>
   </si>
   <si>
-    <t>ti2_8</t>
-  </si>
-  <si>
-    <t>ti3_8</t>
-  </si>
-  <si>
-    <t>ti4_8</t>
-  </si>
-  <si>
     <t>ti1_9</t>
   </si>
   <si>
-    <t>ti2_9</t>
-  </si>
-  <si>
-    <t>ti3_9</t>
-  </si>
-  <si>
-    <t>ti4_9</t>
-  </si>
-  <si>
     <t>ti1_10</t>
   </si>
   <si>
-    <t>ti2_10</t>
-  </si>
-  <si>
-    <t>ti3_10</t>
-  </si>
-  <si>
-    <t>ti4_10</t>
-  </si>
-  <si>
     <t>ti1_11</t>
   </si>
   <si>
-    <t>ti2_11</t>
-  </si>
-  <si>
-    <t>ti3_11</t>
-  </si>
-  <si>
-    <t>ti4_11</t>
-  </si>
-  <si>
     <t>ti1_12</t>
   </si>
   <si>
-    <t>ti2_12</t>
-  </si>
-  <si>
-    <t>ti3_12</t>
-  </si>
-  <si>
-    <t>ti4_12</t>
-  </si>
-  <si>
     <t>ti1_13</t>
   </si>
   <si>
-    <t>ti2_13</t>
-  </si>
-  <si>
-    <t>ti3_13</t>
-  </si>
-  <si>
-    <t>ti4_13</t>
-  </si>
-  <si>
     <t>ti1_14</t>
   </si>
   <si>
-    <t>ti2_14</t>
-  </si>
-  <si>
-    <t>ti3_14</t>
-  </si>
-  <si>
-    <t>ti4_14</t>
-  </si>
-  <si>
     <t>ti1_15</t>
   </si>
   <si>
-    <t>ti2_15</t>
-  </si>
-  <si>
-    <t>ti3_15</t>
-  </si>
-  <si>
-    <t>ti4_15</t>
-  </si>
-  <si>
     <t>ti1_16</t>
   </si>
   <si>
-    <t>ti2_16</t>
-  </si>
-  <si>
-    <t>ti3_16</t>
-  </si>
-  <si>
-    <t>ti4_16</t>
-  </si>
-  <si>
     <t>ti1_17</t>
   </si>
   <si>
-    <t>ti2_17</t>
-  </si>
-  <si>
-    <t>ti3_17</t>
-  </si>
-  <si>
-    <t>ti4_17</t>
-  </si>
-  <si>
     <t>ti1_18</t>
   </si>
   <si>
-    <t>ti2_18</t>
-  </si>
-  <si>
-    <t>ti3_18</t>
-  </si>
-  <si>
-    <t>ti4_18</t>
-  </si>
-  <si>
     <t>ti1_19</t>
   </si>
   <si>
-    <t>ti2_19</t>
-  </si>
-  <si>
-    <t>ti3_19</t>
-  </si>
-  <si>
-    <t>ti4_19</t>
-  </si>
-  <si>
     <t>ti1_20</t>
   </si>
   <si>
-    <t>ti2_20</t>
-  </si>
-  <si>
-    <t>ti3_20</t>
-  </si>
-  <si>
-    <t>ti4_20</t>
-  </si>
-  <si>
     <t>ti1_21</t>
   </si>
   <si>
-    <t>ti2_21</t>
-  </si>
-  <si>
-    <t>ti3_21</t>
-  </si>
-  <si>
-    <t>ti4_21</t>
-  </si>
-  <si>
     <t>ti1_22</t>
   </si>
   <si>
-    <t>ti2_22</t>
-  </si>
-  <si>
-    <t>ti3_22</t>
-  </si>
-  <si>
-    <t>ti4_22</t>
-  </si>
-  <si>
     <t>± 0,205 мс</t>
   </si>
   <si>
@@ -1297,15 +1099,6 @@
   </si>
   <si>
     <t>DT, (кан. 1)</t>
-  </si>
-  <si>
-    <t>DT, (кан. 2)</t>
-  </si>
-  <si>
-    <t>DT, (кан. 3)</t>
-  </si>
-  <si>
-    <t>DT, (кан. 4)</t>
   </si>
   <si>
     <t>Допустимая DT</t>
@@ -2230,7 +2023,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -2340,17 +2133,65 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2409,50 +2250,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2774,31 +2579,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="68"/>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
+      <c r="A1" s="40"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
     </row>
     <row r="2" spans="1:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="74" t="str">
+      <c r="A3" s="49" t="str">
         <f>"Протокол поверки № 10/"&amp;C161&amp;"/"&amp;C6</f>
         <v>Протокол поверки № 10/_date/_numb</v>
       </c>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="74"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
     </row>
     <row r="4" spans="1:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5"/>
@@ -2811,10 +2616,10 @@
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="B5" s="41"/>
+      <c r="B5" s="46"/>
       <c r="C5" s="10" t="s">
         <v>81</v>
       </c>
@@ -2827,10 +2632,10 @@
       <c r="H5" s="13"/>
     </row>
     <row r="6" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="41" t="s">
+      <c r="A6" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="B6" s="41"/>
+      <c r="B6" s="46"/>
       <c r="C6" s="14" t="s">
         <v>84</v>
       </c>
@@ -2841,38 +2646,38 @@
       <c r="H6" s="13"/>
     </row>
     <row r="7" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="72">
+      <c r="B7" s="46"/>
+      <c r="C7" s="47">
         <v>2012</v>
       </c>
-      <c r="D7" s="72"/>
-      <c r="E7" s="72"/>
-      <c r="F7" s="72"/>
-      <c r="G7" s="72"/>
-      <c r="H7" s="72"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="47"/>
+      <c r="F7" s="47"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="47"/>
     </row>
     <row r="8" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15" t="s">
         <v>86</v>
       </c>
       <c r="B8" s="32"/>
-      <c r="C8" s="73" t="s">
+      <c r="C8" s="48" t="s">
         <v>92</v>
       </c>
-      <c r="D8" s="73"/>
-      <c r="E8" s="73"/>
-      <c r="F8" s="73"/>
-      <c r="G8" s="73"/>
-      <c r="H8" s="73"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
     </row>
     <row r="9" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="41" t="s">
+      <c r="A9" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="B9" s="41"/>
+      <c r="B9" s="46"/>
       <c r="C9" s="14" t="s">
         <v>88</v>
       </c>
@@ -2883,52 +2688,52 @@
       <c r="H9" s="17"/>
     </row>
     <row r="10" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="51" t="s">
+      <c r="A10" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="B10" s="52"/>
-      <c r="C10" s="42" t="s">
+      <c r="B10" s="68"/>
+      <c r="C10" s="58" t="s">
         <v>93</v>
       </c>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="44"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="60"/>
     </row>
     <row r="11" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="53"/>
-      <c r="B11" s="54"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="47"/>
+      <c r="A11" s="69"/>
+      <c r="B11" s="70"/>
+      <c r="C11" s="61"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
+      <c r="G11" s="62"/>
+      <c r="H11" s="63"/>
     </row>
     <row r="12" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="55"/>
-      <c r="B12" s="56"/>
-      <c r="C12" s="48"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="50"/>
+      <c r="A12" s="71"/>
+      <c r="B12" s="72"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="66"/>
     </row>
     <row r="13" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="75" t="s">
+      <c r="A13" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="B13" s="75"/>
-      <c r="C13" s="71" t="s">
+      <c r="B13" s="50"/>
+      <c r="C13" s="45" t="s">
         <v>91</v>
       </c>
-      <c r="D13" s="71"/>
-      <c r="E13" s="71"/>
-      <c r="F13" s="71"/>
-      <c r="G13" s="71"/>
-      <c r="H13" s="71"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="45"/>
     </row>
     <row r="14" spans="1:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5"/>
@@ -2948,96 +2753,96 @@
       <c r="E15" s="2"/>
     </row>
     <row r="16" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="58" t="s">
+      <c r="A16" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="59"/>
-      <c r="C16" s="59"/>
-      <c r="D16" s="60"/>
-      <c r="E16" s="69" t="s">
+      <c r="B16" s="75"/>
+      <c r="C16" s="75"/>
+      <c r="D16" s="76"/>
+      <c r="E16" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="F16" s="70"/>
-      <c r="G16" s="65" t="s">
+      <c r="F16" s="42"/>
+      <c r="G16" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="H16" s="65"/>
+      <c r="H16" s="52"/>
     </row>
     <row r="17" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="63" t="s">
+      <c r="A17" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="63"/>
-      <c r="C17" s="63"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="66" t="s">
+      <c r="B17" s="44"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="53" t="s">
         <v>77</v>
       </c>
-      <c r="F17" s="66"/>
-      <c r="G17" s="62" t="s">
-        <v>296</v>
-      </c>
-      <c r="H17" s="62"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="43" t="s">
+        <v>230</v>
+      </c>
+      <c r="H17" s="43"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="63" t="s">
+      <c r="A18" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="63"/>
-      <c r="C18" s="63"/>
-      <c r="D18" s="63"/>
-      <c r="E18" s="66" t="s">
+      <c r="B18" s="44"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="53" t="s">
         <v>78</v>
       </c>
-      <c r="F18" s="66"/>
-      <c r="G18" s="62" t="s">
-        <v>297</v>
-      </c>
-      <c r="H18" s="62"/>
+      <c r="F18" s="53"/>
+      <c r="G18" s="43" t="s">
+        <v>231</v>
+      </c>
+      <c r="H18" s="43"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="63" t="s">
+      <c r="A19" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="63"/>
-      <c r="C19" s="63"/>
-      <c r="D19" s="63"/>
-      <c r="E19" s="66" t="s">
+      <c r="B19" s="44"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="53" t="s">
         <v>79</v>
       </c>
-      <c r="F19" s="66"/>
-      <c r="G19" s="62" t="s">
-        <v>298</v>
-      </c>
-      <c r="H19" s="62"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="H19" s="43"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="63" t="s">
+      <c r="A20" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="63"/>
-      <c r="C20" s="63"/>
-      <c r="D20" s="63"/>
-      <c r="E20" s="57"/>
-      <c r="F20" s="57"/>
-      <c r="G20" s="62" t="s">
-        <v>299</v>
-      </c>
-      <c r="H20" s="62"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="73"/>
+      <c r="G20" s="43" t="s">
+        <v>233</v>
+      </c>
+      <c r="H20" s="43"/>
     </row>
     <row r="21" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="63" t="s">
+      <c r="A21" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="63"/>
-      <c r="C21" s="63"/>
-      <c r="D21" s="63"/>
-      <c r="E21" s="67"/>
-      <c r="F21" s="67"/>
-      <c r="G21" s="62" t="s">
-        <v>300</v>
-      </c>
-      <c r="H21" s="62"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="57"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="43" t="s">
+        <v>234</v>
+      </c>
+      <c r="H21" s="43"/>
     </row>
     <row r="22" spans="1:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="33"/>
@@ -3143,8 +2948,8 @@
       <c r="F29" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="G29" s="61" t="s">
-        <v>301</v>
+      <c r="G29" s="54" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3166,7 +2971,7 @@
       <c r="F30" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="G30" s="40"/>
+      <c r="G30" s="56"/>
     </row>
     <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
@@ -3187,8 +2992,8 @@
       <c r="F31" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="G31" s="61" t="s">
-        <v>302</v>
+      <c r="G31" s="54" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3210,7 +3015,7 @@
       <c r="F32" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="G32" s="39"/>
+      <c r="G32" s="55"/>
     </row>
     <row r="33" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
@@ -3231,7 +3036,7 @@
       <c r="F33" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="G33" s="39"/>
+      <c r="G33" s="55"/>
     </row>
     <row r="34" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
@@ -3252,7 +3057,7 @@
       <c r="F34" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="G34" s="39"/>
+      <c r="G34" s="55"/>
     </row>
     <row r="35" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
@@ -3273,7 +3078,7 @@
       <c r="F35" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="G35" s="39"/>
+      <c r="G35" s="55"/>
     </row>
     <row r="36" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
@@ -3294,7 +3099,7 @@
       <c r="F36" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="G36" s="39"/>
+      <c r="G36" s="55"/>
     </row>
     <row r="37" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
@@ -3315,7 +3120,7 @@
       <c r="F37" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="G37" s="39"/>
+      <c r="G37" s="55"/>
     </row>
     <row r="38" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
@@ -3336,7 +3141,7 @@
       <c r="F38" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="G38" s="39"/>
+      <c r="G38" s="55"/>
     </row>
     <row r="39" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
@@ -3357,7 +3162,7 @@
       <c r="F39" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="G39" s="40"/>
+      <c r="G39" s="56"/>
     </row>
     <row r="40" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="41" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3406,8 +3211,8 @@
       <c r="E43" s="31" t="s">
         <v>147</v>
       </c>
-      <c r="F43" s="39" t="s">
-        <v>324</v>
+      <c r="F43" s="55" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3426,7 +3231,7 @@
       <c r="E44" s="31" t="s">
         <v>151</v>
       </c>
-      <c r="F44" s="39"/>
+      <c r="F44" s="55"/>
     </row>
     <row r="45" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="21">
@@ -3444,7 +3249,7 @@
       <c r="E45" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="F45" s="39"/>
+      <c r="F45" s="55"/>
     </row>
     <row r="46" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="21">
@@ -3462,7 +3267,7 @@
       <c r="E46" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="F46" s="39"/>
+      <c r="F46" s="55"/>
     </row>
     <row r="47" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="21">
@@ -3480,7 +3285,7 @@
       <c r="E47" s="31" t="s">
         <v>163</v>
       </c>
-      <c r="F47" s="39"/>
+      <c r="F47" s="55"/>
     </row>
     <row r="48" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="22">
@@ -3498,7 +3303,7 @@
       <c r="E48" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="F48" s="39"/>
+      <c r="F48" s="55"/>
     </row>
     <row r="49" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="22">
@@ -3516,7 +3321,7 @@
       <c r="E49" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="F49" s="39"/>
+      <c r="F49" s="55"/>
     </row>
     <row r="50" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="22">
@@ -3534,7 +3339,7 @@
       <c r="E50" s="31" t="s">
         <v>175</v>
       </c>
-      <c r="F50" s="39"/>
+      <c r="F50" s="55"/>
     </row>
     <row r="51" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="20">
@@ -3552,7 +3357,7 @@
       <c r="E51" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="F51" s="39"/>
+      <c r="F51" s="55"/>
     </row>
     <row r="52" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="20">
@@ -3570,7 +3375,7 @@
       <c r="E52" s="31" t="s">
         <v>183</v>
       </c>
-      <c r="F52" s="40"/>
+      <c r="F52" s="56"/>
     </row>
     <row r="53" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="26" t="s">
@@ -3580,10 +3385,10 @@
         <v>16</v>
       </c>
       <c r="C53" s="30" t="s">
-        <v>325</v>
+        <v>256</v>
       </c>
       <c r="D53" s="30" t="s">
-        <v>326</v>
+        <v>257</v>
       </c>
       <c r="E53" s="30" t="s">
         <v>34</v>
@@ -3592,941 +3397,941 @@
         <v>35</v>
       </c>
       <c r="G53" s="24" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="H53" s="26" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="62">
+      <c r="A54" s="43">
         <v>1</v>
       </c>
       <c r="B54" s="4">
         <v>5</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>328</v>
+        <v>259</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>329</v>
+        <v>260</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>330</v>
+        <v>261</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>331</v>
+        <v>262</v>
       </c>
       <c r="G54" s="9" t="e">
         <f>20*LOG10((E54/F54)/(C54/D54))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H54" s="62" t="s">
-        <v>302</v>
+      <c r="H54" s="43" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="62"/>
+      <c r="A55" s="43"/>
       <c r="B55" s="4">
         <v>10</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>332</v>
+        <v>263</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>333</v>
+        <v>264</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>334</v>
+        <v>265</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>335</v>
+        <v>266</v>
       </c>
       <c r="G55" s="9" t="e">
         <f t="shared" ref="G55:G93" si="0">20*LOG10((E55/F55)/(C55/D55))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H55" s="62"/>
+      <c r="H55" s="43"/>
     </row>
     <row r="56" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="62"/>
+      <c r="A56" s="43"/>
       <c r="B56" s="4">
         <v>20</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>336</v>
+        <v>267</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>337</v>
+        <v>268</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>338</v>
+        <v>269</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>339</v>
+        <v>270</v>
       </c>
       <c r="G56" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H56" s="62"/>
+      <c r="H56" s="43"/>
     </row>
     <row r="57" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="62"/>
+      <c r="A57" s="43"/>
       <c r="B57" s="4">
         <v>50</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>340</v>
+        <v>271</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>341</v>
+        <v>272</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>342</v>
+        <v>273</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>343</v>
+        <v>274</v>
       </c>
       <c r="G57" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H57" s="62"/>
+      <c r="H57" s="43"/>
     </row>
     <row r="58" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="62"/>
+      <c r="A58" s="43"/>
       <c r="B58" s="4">
         <v>100</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>344</v>
+        <v>275</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>345</v>
+        <v>276</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>346</v>
+        <v>277</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>347</v>
+        <v>278</v>
       </c>
       <c r="G58" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H58" s="62"/>
+      <c r="H58" s="43"/>
     </row>
     <row r="59" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="62"/>
+      <c r="A59" s="43"/>
       <c r="B59" s="4">
         <v>200</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>348</v>
+        <v>279</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>349</v>
+        <v>280</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>350</v>
+        <v>281</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>351</v>
+        <v>282</v>
       </c>
       <c r="G59" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H59" s="62"/>
+      <c r="H59" s="43"/>
     </row>
     <row r="60" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="62"/>
+      <c r="A60" s="43"/>
       <c r="B60" s="4">
         <v>500</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>352</v>
+        <v>283</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>353</v>
+        <v>284</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>354</v>
+        <v>285</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>355</v>
+        <v>286</v>
       </c>
       <c r="G60" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H60" s="62"/>
+      <c r="H60" s="43"/>
     </row>
     <row r="61" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="62"/>
+      <c r="A61" s="43"/>
       <c r="B61" s="4">
         <v>1000</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>356</v>
+        <v>287</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>357</v>
+        <v>288</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>358</v>
+        <v>289</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="G61" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H61" s="62"/>
+      <c r="H61" s="43"/>
     </row>
     <row r="62" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="62"/>
+      <c r="A62" s="43"/>
       <c r="B62" s="4">
         <v>2000</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>360</v>
+        <v>291</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>361</v>
+        <v>292</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>362</v>
+        <v>293</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>363</v>
+        <v>294</v>
       </c>
       <c r="G62" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H62" s="62"/>
+      <c r="H62" s="43"/>
     </row>
     <row r="63" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="62"/>
+      <c r="A63" s="43"/>
       <c r="B63" s="4">
         <v>5000</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>364</v>
+        <v>295</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>365</v>
+        <v>296</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>366</v>
+        <v>297</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>367</v>
+        <v>298</v>
       </c>
       <c r="G63" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H63" s="62"/>
+      <c r="H63" s="43"/>
     </row>
     <row r="64" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="62">
+      <c r="A64" s="43">
         <v>2</v>
       </c>
       <c r="B64" s="4">
         <v>5</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>368</v>
+        <v>299</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>369</v>
+        <v>300</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>370</v>
+        <v>301</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>371</v>
+        <v>302</v>
       </c>
       <c r="G64" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H64" s="62"/>
+      <c r="H64" s="43"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="62"/>
+      <c r="A65" s="43"/>
       <c r="B65" s="4">
         <v>10</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>372</v>
+        <v>303</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>373</v>
+        <v>304</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>374</v>
+        <v>305</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>375</v>
+        <v>306</v>
       </c>
       <c r="G65" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H65" s="62"/>
+      <c r="H65" s="43"/>
     </row>
     <row r="66" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="62"/>
+      <c r="A66" s="43"/>
       <c r="B66" s="4">
         <v>20</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>376</v>
+        <v>307</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>377</v>
+        <v>308</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>378</v>
+        <v>309</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>379</v>
+        <v>310</v>
       </c>
       <c r="G66" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H66" s="62"/>
+      <c r="H66" s="43"/>
     </row>
     <row r="67" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="62"/>
+      <c r="A67" s="43"/>
       <c r="B67" s="4">
         <v>50</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>380</v>
+        <v>311</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>381</v>
+        <v>312</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>382</v>
+        <v>313</v>
       </c>
       <c r="F67" s="9" t="s">
-        <v>383</v>
+        <v>314</v>
       </c>
       <c r="G67" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H67" s="62"/>
+      <c r="H67" s="43"/>
     </row>
     <row r="68" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="62"/>
+      <c r="A68" s="43"/>
       <c r="B68" s="4">
         <v>100</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>384</v>
+        <v>315</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>385</v>
+        <v>316</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>386</v>
+        <v>317</v>
       </c>
       <c r="F68" s="9" t="s">
-        <v>387</v>
+        <v>318</v>
       </c>
       <c r="G68" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H68" s="62"/>
+      <c r="H68" s="43"/>
     </row>
     <row r="69" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="62"/>
+      <c r="A69" s="43"/>
       <c r="B69" s="4">
         <v>200</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>388</v>
+        <v>319</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>389</v>
+        <v>320</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>390</v>
+        <v>321</v>
       </c>
       <c r="F69" s="9" t="s">
-        <v>391</v>
+        <v>322</v>
       </c>
       <c r="G69" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H69" s="62"/>
+      <c r="H69" s="43"/>
     </row>
     <row r="70" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="62"/>
+      <c r="A70" s="43"/>
       <c r="B70" s="4">
         <v>500</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>392</v>
+        <v>323</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>393</v>
+        <v>324</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>394</v>
+        <v>325</v>
       </c>
       <c r="F70" s="9" t="s">
-        <v>395</v>
+        <v>326</v>
       </c>
       <c r="G70" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H70" s="62"/>
+      <c r="H70" s="43"/>
     </row>
     <row r="71" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="62"/>
+      <c r="A71" s="43"/>
       <c r="B71" s="4">
         <v>1000</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>396</v>
+        <v>327</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>397</v>
+        <v>328</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>398</v>
+        <v>329</v>
       </c>
       <c r="F71" s="9" t="s">
-        <v>399</v>
+        <v>330</v>
       </c>
       <c r="G71" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H71" s="62"/>
+      <c r="H71" s="43"/>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="62"/>
+      <c r="A72" s="43"/>
       <c r="B72" s="4">
         <v>2000</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>400</v>
+        <v>331</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>401</v>
+        <v>332</v>
       </c>
       <c r="E72" s="9" t="s">
-        <v>402</v>
+        <v>333</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>403</v>
+        <v>334</v>
       </c>
       <c r="G72" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H72" s="62"/>
+      <c r="H72" s="43"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="62"/>
+      <c r="A73" s="43"/>
       <c r="B73" s="4">
         <v>5000</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>404</v>
+        <v>335</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>405</v>
+        <v>336</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>406</v>
+        <v>337</v>
       </c>
       <c r="F73" s="9" t="s">
-        <v>407</v>
+        <v>338</v>
       </c>
       <c r="G73" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H73" s="62"/>
+      <c r="H73" s="43"/>
     </row>
     <row r="74" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="62">
+      <c r="A74" s="43">
         <v>3</v>
       </c>
       <c r="B74" s="4">
         <v>5</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>408</v>
+        <v>339</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>409</v>
+        <v>340</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>410</v>
+        <v>341</v>
       </c>
       <c r="F74" s="9" t="s">
-        <v>411</v>
+        <v>342</v>
       </c>
       <c r="G74" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H74" s="62"/>
+      <c r="H74" s="43"/>
     </row>
     <row r="75" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="62"/>
+      <c r="A75" s="43"/>
       <c r="B75" s="4">
         <v>10</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>412</v>
+        <v>343</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>413</v>
+        <v>344</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>414</v>
+        <v>345</v>
       </c>
       <c r="F75" s="9" t="s">
-        <v>415</v>
+        <v>346</v>
       </c>
       <c r="G75" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H75" s="62"/>
+      <c r="H75" s="43"/>
     </row>
     <row r="76" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="62"/>
+      <c r="A76" s="43"/>
       <c r="B76" s="4">
         <v>20</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>416</v>
+        <v>347</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>417</v>
+        <v>348</v>
       </c>
       <c r="E76" s="9" t="s">
-        <v>418</v>
+        <v>349</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>419</v>
+        <v>350</v>
       </c>
       <c r="G76" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H76" s="62"/>
+      <c r="H76" s="43"/>
     </row>
     <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="62"/>
+      <c r="A77" s="43"/>
       <c r="B77" s="4">
         <v>50</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>420</v>
+        <v>351</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>421</v>
+        <v>352</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>422</v>
+        <v>353</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>423</v>
+        <v>354</v>
       </c>
       <c r="G77" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H77" s="62"/>
+      <c r="H77" s="43"/>
     </row>
     <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="62"/>
+      <c r="A78" s="43"/>
       <c r="B78" s="4">
         <v>100</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>424</v>
+        <v>355</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>425</v>
+        <v>356</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>426</v>
+        <v>357</v>
       </c>
       <c r="F78" s="9" t="s">
-        <v>427</v>
+        <v>358</v>
       </c>
       <c r="G78" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H78" s="62"/>
+      <c r="H78" s="43"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="62"/>
+      <c r="A79" s="43"/>
       <c r="B79" s="4">
         <v>200</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>428</v>
+        <v>359</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>429</v>
+        <v>360</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>430</v>
+        <v>361</v>
       </c>
       <c r="F79" s="9" t="s">
-        <v>431</v>
+        <v>362</v>
       </c>
       <c r="G79" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H79" s="62"/>
+      <c r="H79" s="43"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="62"/>
+      <c r="A80" s="43"/>
       <c r="B80" s="4">
         <v>500</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>432</v>
+        <v>363</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>433</v>
+        <v>364</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>434</v>
+        <v>365</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>435</v>
+        <v>366</v>
       </c>
       <c r="G80" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H80" s="62"/>
+      <c r="H80" s="43"/>
     </row>
     <row r="81" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="62"/>
+      <c r="A81" s="43"/>
       <c r="B81" s="4">
         <v>1000</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>436</v>
+        <v>367</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>437</v>
+        <v>368</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>438</v>
+        <v>369</v>
       </c>
       <c r="F81" s="9" t="s">
-        <v>439</v>
+        <v>370</v>
       </c>
       <c r="G81" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H81" s="62"/>
+      <c r="H81" s="43"/>
     </row>
     <row r="82" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="62"/>
+      <c r="A82" s="43"/>
       <c r="B82" s="4">
         <v>2000</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>440</v>
+        <v>371</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>441</v>
+        <v>372</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>442</v>
+        <v>373</v>
       </c>
       <c r="F82" s="9" t="s">
-        <v>443</v>
+        <v>374</v>
       </c>
       <c r="G82" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H82" s="62"/>
+      <c r="H82" s="43"/>
     </row>
     <row r="83" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="62"/>
+      <c r="A83" s="43"/>
       <c r="B83" s="4">
         <v>5000</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>444</v>
+        <v>375</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>445</v>
+        <v>376</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>446</v>
+        <v>377</v>
       </c>
       <c r="F83" s="9" t="s">
-        <v>447</v>
+        <v>378</v>
       </c>
       <c r="G83" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H83" s="62"/>
+      <c r="H83" s="43"/>
     </row>
     <row r="84" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="62">
+      <c r="A84" s="43">
         <v>4</v>
       </c>
       <c r="B84" s="4">
         <v>5</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>448</v>
+        <v>379</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>449</v>
+        <v>380</v>
       </c>
       <c r="E84" s="9" t="s">
-        <v>450</v>
+        <v>381</v>
       </c>
       <c r="F84" s="9" t="s">
-        <v>451</v>
+        <v>382</v>
       </c>
       <c r="G84" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H84" s="62"/>
+      <c r="H84" s="43"/>
     </row>
     <row r="85" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="62"/>
+      <c r="A85" s="43"/>
       <c r="B85" s="4">
         <v>10</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>452</v>
+        <v>383</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>453</v>
+        <v>384</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>454</v>
+        <v>385</v>
       </c>
       <c r="F85" s="9" t="s">
-        <v>455</v>
+        <v>386</v>
       </c>
       <c r="G85" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H85" s="62"/>
+      <c r="H85" s="43"/>
     </row>
     <row r="86" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="62"/>
+      <c r="A86" s="43"/>
       <c r="B86" s="4">
         <v>20</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>456</v>
+        <v>387</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>457</v>
+        <v>388</v>
       </c>
       <c r="E86" s="9" t="s">
-        <v>458</v>
+        <v>389</v>
       </c>
       <c r="F86" s="9" t="s">
-        <v>459</v>
+        <v>390</v>
       </c>
       <c r="G86" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H86" s="62"/>
+      <c r="H86" s="43"/>
     </row>
     <row r="87" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="62"/>
+      <c r="A87" s="43"/>
       <c r="B87" s="4">
         <v>50</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>460</v>
+        <v>391</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>461</v>
+        <v>392</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>462</v>
+        <v>393</v>
       </c>
       <c r="F87" s="9" t="s">
-        <v>463</v>
+        <v>394</v>
       </c>
       <c r="G87" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H87" s="62"/>
+      <c r="H87" s="43"/>
     </row>
     <row r="88" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="62"/>
+      <c r="A88" s="43"/>
       <c r="B88" s="4">
         <v>100</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>464</v>
+        <v>395</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>465</v>
+        <v>396</v>
       </c>
       <c r="E88" s="9" t="s">
-        <v>466</v>
+        <v>397</v>
       </c>
       <c r="F88" s="9" t="s">
-        <v>467</v>
+        <v>398</v>
       </c>
       <c r="G88" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H88" s="62"/>
+      <c r="H88" s="43"/>
     </row>
     <row r="89" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="62"/>
+      <c r="A89" s="43"/>
       <c r="B89" s="4">
         <v>200</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>468</v>
+        <v>399</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>469</v>
+        <v>400</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>470</v>
+        <v>401</v>
       </c>
       <c r="F89" s="9" t="s">
-        <v>471</v>
+        <v>402</v>
       </c>
       <c r="G89" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H89" s="62"/>
+      <c r="H89" s="43"/>
     </row>
     <row r="90" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="62"/>
+      <c r="A90" s="43"/>
       <c r="B90" s="4">
         <v>500</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>472</v>
+        <v>403</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>473</v>
+        <v>404</v>
       </c>
       <c r="E90" s="9" t="s">
-        <v>474</v>
+        <v>405</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>475</v>
+        <v>406</v>
       </c>
       <c r="G90" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H90" s="62"/>
+      <c r="H90" s="43"/>
     </row>
     <row r="91" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="62"/>
+      <c r="A91" s="43"/>
       <c r="B91" s="4">
         <v>1000</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>476</v>
+        <v>407</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>477</v>
+        <v>408</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>478</v>
+        <v>409</v>
       </c>
       <c r="F91" s="9" t="s">
-        <v>479</v>
+        <v>410</v>
       </c>
       <c r="G91" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H91" s="62"/>
+      <c r="H91" s="43"/>
     </row>
     <row r="92" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="62"/>
+      <c r="A92" s="43"/>
       <c r="B92" s="4">
         <v>2000</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>480</v>
+        <v>411</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>481</v>
+        <v>412</v>
       </c>
       <c r="E92" s="9" t="s">
-        <v>482</v>
+        <v>413</v>
       </c>
       <c r="F92" s="9" t="s">
-        <v>483</v>
+        <v>414</v>
       </c>
       <c r="G92" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H92" s="62"/>
+      <c r="H92" s="43"/>
     </row>
     <row r="93" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="62"/>
+      <c r="A93" s="43"/>
       <c r="B93" s="4">
         <v>5000</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>484</v>
+        <v>415</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>485</v>
+        <v>416</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>486</v>
+        <v>417</v>
       </c>
       <c r="F93" s="9" t="s">
-        <v>487</v>
+        <v>418</v>
       </c>
       <c r="G93" s="9" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H93" s="62"/>
+      <c r="H93" s="43"/>
     </row>
     <row r="94" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="29"/>
@@ -4586,20 +4391,14 @@
         <v>3</v>
       </c>
       <c r="B99" s="30" t="s">
-        <v>303</v>
-      </c>
-      <c r="C99" s="30" t="s">
-        <v>304</v>
-      </c>
-      <c r="D99" s="30" t="s">
-        <v>305</v>
-      </c>
-      <c r="E99" s="30" t="s">
-        <v>306</v>
-      </c>
-      <c r="F99" s="30" t="s">
-        <v>307</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="C99" s="39" t="s">
+        <v>238</v>
+      </c>
+      <c r="D99" s="78"/>
+      <c r="E99" s="78"/>
+      <c r="F99" s="78"/>
     </row>
     <row r="100" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="26" t="s">
@@ -4608,458 +4407,320 @@
       <c r="B100" s="23" t="s">
         <v>186</v>
       </c>
-      <c r="C100" s="23" t="s">
-        <v>187</v>
-      </c>
-      <c r="D100" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="E100" s="23" t="s">
-        <v>189</v>
-      </c>
-      <c r="F100" s="26" t="s">
-        <v>274</v>
-      </c>
+      <c r="C100" s="38" t="s">
+        <v>208</v>
+      </c>
+      <c r="D100" s="79"/>
+      <c r="E100" s="79"/>
+      <c r="F100" s="6"/>
     </row>
     <row r="101" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="26" t="s">
         <v>39</v>
       </c>
       <c r="B101" s="23" t="s">
-        <v>190</v>
-      </c>
-      <c r="C101" s="23" t="s">
-        <v>191</v>
-      </c>
-      <c r="D101" s="23" t="s">
-        <v>192</v>
-      </c>
-      <c r="E101" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="F101" s="26" t="s">
-        <v>275</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="C101" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="D101" s="79"/>
+      <c r="E101" s="79"/>
+      <c r="F101" s="6"/>
     </row>
     <row r="102" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="26" t="s">
         <v>40</v>
       </c>
       <c r="B102" s="23" t="s">
-        <v>194</v>
-      </c>
-      <c r="C102" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="D102" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="E102" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="F102" s="26" t="s">
-        <v>276</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="C102" s="38" t="s">
+        <v>210</v>
+      </c>
+      <c r="D102" s="79"/>
+      <c r="E102" s="79"/>
+      <c r="F102" s="6"/>
     </row>
     <row r="103" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="26" t="s">
         <v>68</v>
       </c>
       <c r="B103" s="23" t="s">
-        <v>198</v>
-      </c>
-      <c r="C103" s="23" t="s">
-        <v>199</v>
-      </c>
-      <c r="D103" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="E103" s="23" t="s">
-        <v>201</v>
-      </c>
-      <c r="F103" s="26" t="s">
-        <v>277</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="C103" s="38" t="s">
+        <v>211</v>
+      </c>
+      <c r="D103" s="79"/>
+      <c r="E103" s="79"/>
+      <c r="F103" s="6"/>
     </row>
     <row r="104" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="26" t="s">
         <v>42</v>
       </c>
       <c r="B104" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="C104" s="23" t="s">
-        <v>203</v>
-      </c>
-      <c r="D104" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="E104" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="F104" s="26" t="s">
-        <v>278</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="C104" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="D104" s="79"/>
+      <c r="E104" s="79"/>
+      <c r="F104" s="6"/>
     </row>
     <row r="105" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="26" t="s">
         <v>43</v>
       </c>
       <c r="B105" s="23" t="s">
-        <v>206</v>
-      </c>
-      <c r="C105" s="23" t="s">
-        <v>207</v>
-      </c>
-      <c r="D105" s="23" t="s">
-        <v>208</v>
-      </c>
-      <c r="E105" s="23" t="s">
-        <v>209</v>
-      </c>
-      <c r="F105" s="26" t="s">
-        <v>279</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="C105" s="38" t="s">
+        <v>213</v>
+      </c>
+      <c r="D105" s="79"/>
+      <c r="E105" s="79"/>
+      <c r="F105" s="6"/>
     </row>
     <row r="106" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="26" t="s">
         <v>1</v>
       </c>
       <c r="B106" s="23" t="s">
-        <v>210</v>
-      </c>
-      <c r="C106" s="23" t="s">
-        <v>211</v>
-      </c>
-      <c r="D106" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="E106" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="F106" s="26" t="s">
-        <v>308</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="C106" s="38" t="s">
+        <v>239</v>
+      </c>
+      <c r="D106" s="79"/>
+      <c r="E106" s="79"/>
+      <c r="F106" s="6"/>
     </row>
     <row r="107" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="26" t="s">
         <v>44</v>
       </c>
       <c r="B107" s="23" t="s">
-        <v>214</v>
-      </c>
-      <c r="C107" s="23" t="s">
-        <v>215</v>
-      </c>
-      <c r="D107" s="23" t="s">
-        <v>216</v>
-      </c>
-      <c r="E107" s="23" t="s">
-        <v>217</v>
-      </c>
-      <c r="F107" s="26" t="s">
-        <v>309</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="C107" s="38" t="s">
+        <v>240</v>
+      </c>
+      <c r="D107" s="79"/>
+      <c r="E107" s="79"/>
+      <c r="F107" s="6"/>
     </row>
     <row r="108" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="26" t="s">
         <v>45</v>
       </c>
       <c r="B108" s="23" t="s">
-        <v>218</v>
-      </c>
-      <c r="C108" s="23" t="s">
-        <v>219</v>
-      </c>
-      <c r="D108" s="23" t="s">
-        <v>220</v>
-      </c>
-      <c r="E108" s="23" t="s">
-        <v>221</v>
-      </c>
-      <c r="F108" s="26" t="s">
-        <v>310</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="C108" s="38" t="s">
+        <v>241</v>
+      </c>
+      <c r="D108" s="79"/>
+      <c r="E108" s="79"/>
+      <c r="F108" s="6"/>
     </row>
     <row r="109" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="26" t="s">
         <v>3</v>
       </c>
       <c r="B109" s="30" t="s">
-        <v>303</v>
-      </c>
-      <c r="C109" s="30" t="s">
-        <v>304</v>
-      </c>
-      <c r="D109" s="30" t="s">
-        <v>305</v>
-      </c>
-      <c r="E109" s="30" t="s">
-        <v>306</v>
-      </c>
-      <c r="F109" s="30" t="s">
-        <v>307</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="C109" s="39" t="s">
+        <v>238</v>
+      </c>
+      <c r="D109" s="78"/>
+      <c r="E109" s="78"/>
+      <c r="F109" s="78"/>
     </row>
     <row r="110" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="26" t="s">
         <v>46</v>
       </c>
       <c r="B110" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="C110" s="23" t="s">
-        <v>223</v>
-      </c>
-      <c r="D110" s="23" t="s">
-        <v>224</v>
-      </c>
-      <c r="E110" s="23" t="s">
-        <v>225</v>
-      </c>
-      <c r="F110" s="26" t="s">
-        <v>311</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="C110" s="38" t="s">
+        <v>242</v>
+      </c>
+      <c r="D110" s="79"/>
+      <c r="E110" s="79"/>
+      <c r="F110" s="6"/>
     </row>
     <row r="111" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="26" t="s">
         <v>54</v>
       </c>
       <c r="B111" s="23" t="s">
-        <v>226</v>
-      </c>
-      <c r="C111" s="23" t="s">
-        <v>227</v>
-      </c>
-      <c r="D111" s="23" t="s">
-        <v>228</v>
-      </c>
-      <c r="E111" s="23" t="s">
-        <v>229</v>
-      </c>
-      <c r="F111" s="26" t="s">
-        <v>312</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="C111" s="38" t="s">
+        <v>243</v>
+      </c>
+      <c r="D111" s="79"/>
+      <c r="E111" s="79"/>
+      <c r="F111" s="6"/>
     </row>
     <row r="112" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="26" t="s">
         <v>47</v>
       </c>
       <c r="B112" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="C112" s="23" t="s">
-        <v>231</v>
-      </c>
-      <c r="D112" s="23" t="s">
-        <v>232</v>
-      </c>
-      <c r="E112" s="23" t="s">
-        <v>233</v>
-      </c>
-      <c r="F112" s="26" t="s">
-        <v>313</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="C112" s="38" t="s">
+        <v>244</v>
+      </c>
+      <c r="D112" s="79"/>
+      <c r="E112" s="79"/>
+      <c r="F112" s="6"/>
     </row>
     <row r="113" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="26" t="s">
         <v>48</v>
       </c>
       <c r="B113" s="23" t="s">
-        <v>234</v>
-      </c>
-      <c r="C113" s="23" t="s">
-        <v>235</v>
-      </c>
-      <c r="D113" s="23" t="s">
-        <v>236</v>
-      </c>
-      <c r="E113" s="23" t="s">
-        <v>237</v>
-      </c>
-      <c r="F113" s="26" t="s">
-        <v>314</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="C113" s="38" t="s">
+        <v>245</v>
+      </c>
+      <c r="D113" s="79"/>
+      <c r="E113" s="79"/>
+      <c r="F113" s="6"/>
     </row>
     <row r="114" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="26" t="s">
         <v>49</v>
       </c>
       <c r="B114" s="23" t="s">
-        <v>238</v>
-      </c>
-      <c r="C114" s="23" t="s">
-        <v>239</v>
-      </c>
-      <c r="D114" s="23" t="s">
-        <v>240</v>
-      </c>
-      <c r="E114" s="23" t="s">
-        <v>241</v>
-      </c>
-      <c r="F114" s="26" t="s">
-        <v>315</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="C114" s="38" t="s">
+        <v>246</v>
+      </c>
+      <c r="D114" s="79"/>
+      <c r="E114" s="79"/>
+      <c r="F114" s="6"/>
     </row>
     <row r="115" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="26" t="s">
         <v>50</v>
       </c>
       <c r="B115" s="23" t="s">
-        <v>242</v>
-      </c>
-      <c r="C115" s="23" t="s">
-        <v>243</v>
-      </c>
-      <c r="D115" s="23" t="s">
-        <v>244</v>
-      </c>
-      <c r="E115" s="23" t="s">
-        <v>245</v>
-      </c>
-      <c r="F115" s="26" t="s">
-        <v>316</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="C115" s="38" t="s">
+        <v>247</v>
+      </c>
+      <c r="D115" s="79"/>
+      <c r="E115" s="79"/>
+      <c r="F115" s="6"/>
     </row>
     <row r="116" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="26" t="s">
         <v>51</v>
       </c>
       <c r="B116" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="C116" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="D116" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="C116" s="38" t="s">
         <v>248</v>
       </c>
-      <c r="E116" s="23" t="s">
-        <v>249</v>
-      </c>
-      <c r="F116" s="26" t="s">
-        <v>317</v>
-      </c>
+      <c r="D116" s="79"/>
+      <c r="E116" s="79"/>
+      <c r="F116" s="6"/>
     </row>
     <row r="117" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="26" t="s">
         <v>52</v>
       </c>
       <c r="B117" s="23" t="s">
-        <v>250</v>
-      </c>
-      <c r="C117" s="23" t="s">
-        <v>251</v>
-      </c>
-      <c r="D117" s="23" t="s">
-        <v>252</v>
-      </c>
-      <c r="E117" s="23" t="s">
-        <v>253</v>
-      </c>
-      <c r="F117" s="26" t="s">
-        <v>318</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="C117" s="38" t="s">
+        <v>249</v>
+      </c>
+      <c r="D117" s="79"/>
+      <c r="E117" s="79"/>
+      <c r="F117" s="6"/>
     </row>
     <row r="118" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="26" t="s">
         <v>53</v>
       </c>
       <c r="B118" s="23" t="s">
-        <v>254</v>
-      </c>
-      <c r="C118" s="23" t="s">
-        <v>255</v>
-      </c>
-      <c r="D118" s="23" t="s">
-        <v>256</v>
-      </c>
-      <c r="E118" s="23" t="s">
-        <v>257</v>
-      </c>
-      <c r="F118" s="26" t="s">
-        <v>319</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="C118" s="38" t="s">
+        <v>250</v>
+      </c>
+      <c r="D118" s="79"/>
+      <c r="E118" s="79"/>
+      <c r="F118" s="6"/>
     </row>
     <row r="119" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="26" t="s">
         <v>0</v>
       </c>
       <c r="B119" s="23" t="s">
-        <v>258</v>
-      </c>
-      <c r="C119" s="23" t="s">
-        <v>259</v>
-      </c>
-      <c r="D119" s="23" t="s">
-        <v>260</v>
-      </c>
-      <c r="E119" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="F119" s="26" t="s">
-        <v>291</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="C119" s="38" t="s">
+        <v>225</v>
+      </c>
+      <c r="D119" s="79"/>
+      <c r="E119" s="79"/>
+      <c r="F119" s="6"/>
     </row>
     <row r="120" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="26" t="s">
         <v>55</v>
       </c>
       <c r="B120" s="23" t="s">
-        <v>262</v>
-      </c>
-      <c r="C120" s="23" t="s">
-        <v>263</v>
-      </c>
-      <c r="D120" s="23" t="s">
-        <v>264</v>
-      </c>
-      <c r="E120" s="23" t="s">
-        <v>265</v>
-      </c>
-      <c r="F120" s="26" t="s">
-        <v>320</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="C120" s="38" t="s">
+        <v>251</v>
+      </c>
+      <c r="D120" s="79"/>
+      <c r="E120" s="79"/>
+      <c r="F120" s="6"/>
     </row>
     <row r="121" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="26" t="s">
         <v>56</v>
       </c>
       <c r="B121" s="23" t="s">
-        <v>266</v>
-      </c>
-      <c r="C121" s="23" t="s">
-        <v>267</v>
-      </c>
-      <c r="D121" s="23" t="s">
-        <v>268</v>
-      </c>
-      <c r="E121" s="23" t="s">
-        <v>269</v>
-      </c>
-      <c r="F121" s="26" t="s">
-        <v>321</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="C121" s="38" t="s">
+        <v>252</v>
+      </c>
+      <c r="D121" s="79"/>
+      <c r="E121" s="79"/>
+      <c r="F121" s="6"/>
     </row>
     <row r="122" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="26" t="s">
         <v>57</v>
       </c>
       <c r="B122" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="C122" s="23" t="s">
-        <v>271</v>
-      </c>
-      <c r="D122" s="23" t="s">
-        <v>272</v>
-      </c>
-      <c r="E122" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="F122" s="26" t="s">
-        <v>322</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="C122" s="38" t="s">
+        <v>253</v>
+      </c>
+      <c r="D122" s="79"/>
+      <c r="E122" s="79"/>
+      <c r="F122" s="6"/>
     </row>
     <row r="123" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="6"/>
@@ -5089,20 +4750,14 @@
         <v>3</v>
       </c>
       <c r="B126" s="30" t="s">
-        <v>303</v>
-      </c>
-      <c r="C126" s="30" t="s">
-        <v>304</v>
-      </c>
-      <c r="D126" s="30" t="s">
-        <v>305</v>
-      </c>
-      <c r="E126" s="30" t="s">
-        <v>306</v>
-      </c>
-      <c r="F126" s="30" t="s">
-        <v>323</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="C126" s="39" t="s">
+        <v>254</v>
+      </c>
+      <c r="D126" s="78"/>
+      <c r="E126" s="78"/>
+      <c r="F126" s="78"/>
     </row>
     <row r="127" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="26" t="s">
@@ -5111,438 +4766,306 @@
       <c r="B127" s="23" t="s">
         <v>186</v>
       </c>
-      <c r="C127" s="23" t="s">
-        <v>187</v>
-      </c>
-      <c r="D127" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="E127" s="23" t="s">
-        <v>189</v>
-      </c>
-      <c r="F127" s="26" t="s">
-        <v>274</v>
-      </c>
+      <c r="C127" s="38" t="s">
+        <v>208</v>
+      </c>
+      <c r="D127" s="79"/>
+      <c r="E127" s="79"/>
+      <c r="F127" s="6"/>
     </row>
     <row r="128" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="26" t="s">
         <v>39</v>
       </c>
       <c r="B128" s="23" t="s">
-        <v>190</v>
-      </c>
-      <c r="C128" s="23" t="s">
-        <v>191</v>
-      </c>
-      <c r="D128" s="23" t="s">
-        <v>192</v>
-      </c>
-      <c r="E128" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="F128" s="26" t="s">
-        <v>275</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="C128" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="D128" s="79"/>
+      <c r="E128" s="79"/>
+      <c r="F128" s="6"/>
     </row>
     <row r="129" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="26" t="s">
         <v>40</v>
       </c>
       <c r="B129" s="23" t="s">
-        <v>194</v>
-      </c>
-      <c r="C129" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="D129" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="E129" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="F129" s="26" t="s">
-        <v>276</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="C129" s="38" t="s">
+        <v>210</v>
+      </c>
+      <c r="D129" s="79"/>
+      <c r="E129" s="79"/>
+      <c r="F129" s="6"/>
     </row>
     <row r="130" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="26" t="s">
         <v>41</v>
       </c>
       <c r="B130" s="23" t="s">
-        <v>198</v>
-      </c>
-      <c r="C130" s="23" t="s">
-        <v>199</v>
-      </c>
-      <c r="D130" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="E130" s="23" t="s">
-        <v>201</v>
-      </c>
-      <c r="F130" s="26" t="s">
-        <v>277</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="C130" s="38" t="s">
+        <v>211</v>
+      </c>
+      <c r="D130" s="79"/>
+      <c r="E130" s="79"/>
+      <c r="F130" s="6"/>
     </row>
     <row r="131" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="26" t="s">
         <v>42</v>
       </c>
       <c r="B131" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="C131" s="23" t="s">
-        <v>203</v>
-      </c>
-      <c r="D131" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="E131" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="F131" s="26" t="s">
-        <v>278</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="C131" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="D131" s="79"/>
+      <c r="E131" s="79"/>
+      <c r="F131" s="6"/>
     </row>
     <row r="132" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="26" t="s">
         <v>43</v>
       </c>
       <c r="B132" s="23" t="s">
-        <v>206</v>
-      </c>
-      <c r="C132" s="23" t="s">
-        <v>207</v>
-      </c>
-      <c r="D132" s="23" t="s">
-        <v>208</v>
-      </c>
-      <c r="E132" s="23" t="s">
-        <v>209</v>
-      </c>
-      <c r="F132" s="26" t="s">
-        <v>279</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="C132" s="38" t="s">
+        <v>213</v>
+      </c>
+      <c r="D132" s="79"/>
+      <c r="E132" s="79"/>
+      <c r="F132" s="6"/>
     </row>
     <row r="133" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="26" t="s">
         <v>1</v>
       </c>
       <c r="B133" s="23" t="s">
-        <v>210</v>
-      </c>
-      <c r="C133" s="23" t="s">
-        <v>211</v>
-      </c>
-      <c r="D133" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="E133" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="F133" s="26" t="s">
-        <v>280</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="C133" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="D133" s="79"/>
+      <c r="E133" s="79"/>
+      <c r="F133" s="6"/>
     </row>
     <row r="134" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="26" t="s">
         <v>44</v>
       </c>
       <c r="B134" s="23" t="s">
-        <v>214</v>
-      </c>
-      <c r="C134" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="C134" s="38" t="s">
         <v>215</v>
       </c>
-      <c r="D134" s="23" t="s">
-        <v>216</v>
-      </c>
-      <c r="E134" s="23" t="s">
-        <v>217</v>
-      </c>
-      <c r="F134" s="26" t="s">
-        <v>281</v>
-      </c>
+      <c r="D134" s="79"/>
+      <c r="E134" s="79"/>
+      <c r="F134" s="6"/>
     </row>
     <row r="135" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="26" t="s">
         <v>45</v>
       </c>
       <c r="B135" s="23" t="s">
-        <v>218</v>
-      </c>
-      <c r="C135" s="23" t="s">
-        <v>219</v>
-      </c>
-      <c r="D135" s="23" t="s">
-        <v>220</v>
-      </c>
-      <c r="E135" s="23" t="s">
-        <v>221</v>
-      </c>
-      <c r="F135" s="26" t="s">
-        <v>282</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="C135" s="38" t="s">
+        <v>216</v>
+      </c>
+      <c r="D135" s="79"/>
+      <c r="E135" s="79"/>
+      <c r="F135" s="6"/>
     </row>
     <row r="136" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="26" t="s">
         <v>46</v>
       </c>
       <c r="B136" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="C136" s="23" t="s">
-        <v>223</v>
-      </c>
-      <c r="D136" s="23" t="s">
-        <v>224</v>
-      </c>
-      <c r="E136" s="23" t="s">
-        <v>225</v>
-      </c>
-      <c r="F136" s="26" t="s">
-        <v>283</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="C136" s="38" t="s">
+        <v>217</v>
+      </c>
+      <c r="D136" s="79"/>
+      <c r="E136" s="79"/>
+      <c r="F136" s="6"/>
     </row>
     <row r="137" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="26" t="s">
         <v>54</v>
       </c>
       <c r="B137" s="23" t="s">
-        <v>226</v>
-      </c>
-      <c r="C137" s="23" t="s">
-        <v>227</v>
-      </c>
-      <c r="D137" s="23" t="s">
-        <v>228</v>
-      </c>
-      <c r="E137" s="23" t="s">
-        <v>229</v>
-      </c>
-      <c r="F137" s="26" t="s">
-        <v>284</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="C137" s="38" t="s">
+        <v>218</v>
+      </c>
+      <c r="D137" s="79"/>
+      <c r="E137" s="79"/>
+      <c r="F137" s="6"/>
     </row>
     <row r="138" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="26" t="s">
         <v>47</v>
       </c>
       <c r="B138" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="C138" s="23" t="s">
-        <v>231</v>
-      </c>
-      <c r="D138" s="23" t="s">
-        <v>232</v>
-      </c>
-      <c r="E138" s="23" t="s">
-        <v>233</v>
-      </c>
-      <c r="F138" s="26" t="s">
-        <v>285</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="C138" s="38" t="s">
+        <v>219</v>
+      </c>
+      <c r="D138" s="79"/>
+      <c r="E138" s="79"/>
+      <c r="F138" s="6"/>
     </row>
     <row r="139" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="26" t="s">
         <v>48</v>
       </c>
       <c r="B139" s="23" t="s">
-        <v>234</v>
-      </c>
-      <c r="C139" s="23" t="s">
-        <v>235</v>
-      </c>
-      <c r="D139" s="23" t="s">
-        <v>236</v>
-      </c>
-      <c r="E139" s="23" t="s">
-        <v>237</v>
-      </c>
-      <c r="F139" s="26" t="s">
-        <v>286</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="C139" s="38" t="s">
+        <v>220</v>
+      </c>
+      <c r="D139" s="79"/>
+      <c r="E139" s="79"/>
+      <c r="F139" s="6"/>
     </row>
     <row r="140" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="26" t="s">
         <v>49</v>
       </c>
       <c r="B140" s="23" t="s">
-        <v>238</v>
-      </c>
-      <c r="C140" s="23" t="s">
-        <v>239</v>
-      </c>
-      <c r="D140" s="23" t="s">
-        <v>240</v>
-      </c>
-      <c r="E140" s="23" t="s">
-        <v>241</v>
-      </c>
-      <c r="F140" s="26" t="s">
-        <v>287</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="C140" s="38" t="s">
+        <v>221</v>
+      </c>
+      <c r="D140" s="79"/>
+      <c r="E140" s="79"/>
+      <c r="F140" s="6"/>
     </row>
     <row r="141" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="26" t="s">
         <v>50</v>
       </c>
       <c r="B141" s="23" t="s">
-        <v>242</v>
-      </c>
-      <c r="C141" s="23" t="s">
-        <v>243</v>
-      </c>
-      <c r="D141" s="23" t="s">
-        <v>244</v>
-      </c>
-      <c r="E141" s="23" t="s">
-        <v>245</v>
-      </c>
-      <c r="F141" s="26" t="s">
-        <v>288</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="C141" s="38" t="s">
+        <v>222</v>
+      </c>
+      <c r="D141" s="79"/>
+      <c r="E141" s="79"/>
+      <c r="F141" s="6"/>
     </row>
     <row r="142" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="26" t="s">
         <v>51</v>
       </c>
       <c r="B142" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="C142" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="D142" s="23" t="s">
-        <v>248</v>
-      </c>
-      <c r="E142" s="23" t="s">
-        <v>249</v>
-      </c>
-      <c r="F142" s="26" t="s">
-        <v>289</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="C142" s="38" t="s">
+        <v>223</v>
+      </c>
+      <c r="D142" s="79"/>
+      <c r="E142" s="79"/>
+      <c r="F142" s="6"/>
     </row>
     <row r="143" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="26" t="s">
         <v>52</v>
       </c>
       <c r="B143" s="23" t="s">
-        <v>250</v>
-      </c>
-      <c r="C143" s="23" t="s">
-        <v>251</v>
-      </c>
-      <c r="D143" s="23" t="s">
-        <v>252</v>
-      </c>
-      <c r="E143" s="23" t="s">
-        <v>253</v>
-      </c>
-      <c r="F143" s="26" t="s">
-        <v>290</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="C143" s="38" t="s">
+        <v>224</v>
+      </c>
+      <c r="D143" s="79"/>
+      <c r="E143" s="79"/>
+      <c r="F143" s="6"/>
     </row>
     <row r="144" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="26" t="s">
         <v>53</v>
       </c>
       <c r="B144" s="23" t="s">
-        <v>254</v>
-      </c>
-      <c r="C144" s="23" t="s">
-        <v>255</v>
-      </c>
-      <c r="D144" s="23" t="s">
-        <v>256</v>
-      </c>
-      <c r="E144" s="23" t="s">
-        <v>257</v>
-      </c>
-      <c r="F144" s="26" t="s">
-        <v>291</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="C144" s="38" t="s">
+        <v>225</v>
+      </c>
+      <c r="D144" s="79"/>
+      <c r="E144" s="79"/>
+      <c r="F144" s="6"/>
     </row>
     <row r="145" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="26" t="s">
         <v>0</v>
       </c>
       <c r="B145" s="23" t="s">
-        <v>258</v>
-      </c>
-      <c r="C145" s="23" t="s">
-        <v>259</v>
-      </c>
-      <c r="D145" s="23" t="s">
-        <v>260</v>
-      </c>
-      <c r="E145" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="F145" s="26" t="s">
-        <v>292</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="C145" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="D145" s="79"/>
+      <c r="E145" s="79"/>
+      <c r="F145" s="6"/>
     </row>
     <row r="146" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="26" t="s">
         <v>55</v>
       </c>
       <c r="B146" s="23" t="s">
-        <v>262</v>
-      </c>
-      <c r="C146" s="23" t="s">
-        <v>263</v>
-      </c>
-      <c r="D146" s="23" t="s">
-        <v>264</v>
-      </c>
-      <c r="E146" s="23" t="s">
-        <v>265</v>
-      </c>
-      <c r="F146" s="26" t="s">
-        <v>293</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="C146" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="D146" s="79"/>
+      <c r="E146" s="79"/>
+      <c r="F146" s="6"/>
     </row>
     <row r="147" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="26" t="s">
         <v>56</v>
       </c>
       <c r="B147" s="23" t="s">
-        <v>266</v>
-      </c>
-      <c r="C147" s="23" t="s">
-        <v>267</v>
-      </c>
-      <c r="D147" s="23" t="s">
-        <v>268</v>
-      </c>
-      <c r="E147" s="23" t="s">
-        <v>269</v>
-      </c>
-      <c r="F147" s="26" t="s">
-        <v>294</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="C147" s="38" t="s">
+        <v>228</v>
+      </c>
+      <c r="D147" s="79"/>
+      <c r="E147" s="79"/>
+      <c r="F147" s="6"/>
     </row>
     <row r="148" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="26" t="s">
         <v>57</v>
       </c>
       <c r="B148" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="C148" s="23" t="s">
-        <v>271</v>
-      </c>
-      <c r="D148" s="23" t="s">
-        <v>272</v>
-      </c>
-      <c r="E148" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="F148" s="26" t="s">
-        <v>295</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="C148" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="D148" s="79"/>
+      <c r="E148" s="79"/>
+      <c r="F148" s="6"/>
     </row>
     <row r="149" spans="1:8" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="6"/>
@@ -5623,17 +5146,17 @@
     </row>
     <row r="158" spans="1:8" ht="9.6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="159" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A159" s="64" t="s">
+      <c r="A159" s="77" t="s">
         <v>94</v>
       </c>
-      <c r="B159" s="64"/>
+      <c r="B159" s="77"/>
       <c r="C159" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="D159" s="38" t="s">
+      <c r="D159" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="E159" s="38"/>
+      <c r="E159" s="51"/>
       <c r="F159" s="19" t="s">
         <v>97</v>
       </c>
@@ -5642,38 +5165,13 @@
       <c r="B161" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="C161" s="38" t="s">
+      <c r="C161" s="51" t="s">
         <v>99</v>
       </c>
-      <c r="D161" s="38"/>
+      <c r="D161" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="C13:H13"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:H7"/>
-    <mergeCell ref="C8:H8"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="D159:E159"/>
-    <mergeCell ref="H54:H93"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G31:G39"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="E21:F21"/>
     <mergeCell ref="C161:D161"/>
     <mergeCell ref="F43:F52"/>
     <mergeCell ref="A9:B9"/>
@@ -5690,6 +5188,31 @@
     <mergeCell ref="A84:A93"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="A159:B159"/>
+    <mergeCell ref="D159:E159"/>
+    <mergeCell ref="H54:H93"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G31:G39"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="C13:H13"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:H7"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A13:B13"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.78740157480314965" right="0.19685039370078741" top="0.39370078740157483" bottom="0.77083333333333337" header="0.51181102362204722" footer="0.51181102362204722"/>
